--- a/inputs/GRANAR_xml_inputs_generator.xlsx
+++ b/inputs/GRANAR_xml_inputs_generator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2172" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Atkinson et al 2017" sheetId="1" r:id="rId1"/>
@@ -362,34 +362,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -401,6 +386,21 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,21 +802,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
@@ -828,7 +828,7 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="7"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="3">
         <v>1</v>
       </c>
@@ -840,27 +840,27 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
@@ -878,10 +878,10 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="10">
         <v>0.03</v>
       </c>
       <c r="D9" s="3">
@@ -898,10 +898,10 @@
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="10">
         <v>0.01</v>
       </c>
       <c r="D10" s="3">
@@ -914,10 +914,10 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="10">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="D11" s="3">
@@ -930,10 +930,10 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="10">
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="D12" s="3">
@@ -946,20 +946,20 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="15"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="10">
         <v>2.3099999999999999E-2</v>
       </c>
       <c r="D14" s="3">
@@ -970,24 +970,24 @@
         <v>4</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="16"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="10"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="16"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="10">
         <v>2.3199999999999998E-2</v>
       </c>
       <c r="D16" s="3">
@@ -1000,10 +1000,10 @@
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="10">
         <v>2.4299999999999999E-2</v>
       </c>
       <c r="D17" s="3">
@@ -1023,30 +1023,30 @@
       <c r="G18"/>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="4" t="s">
         <v>35</v>
       </c>
@@ -1067,7 +1067,7 @@
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="13" t="s">
         <v>62</v>
       </c>
       <c r="C21" s="3">
@@ -1090,31 +1090,31 @@
       </c>
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11" t="s">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="14"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
@@ -1138,7 +1138,7 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="3">
@@ -1160,21 +1160,21 @@
       </c>
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="6"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
@@ -1186,7 +1186,7 @@
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="3">
@@ -1200,18 +1200,18 @@
       </c>
     </row>
     <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="6"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
@@ -1220,7 +1220,7 @@
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C33" s="3">
@@ -1231,18 +1231,18 @@
       </c>
     </row>
     <row r="35" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="6"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
@@ -1251,7 +1251,7 @@
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="3">
@@ -1262,18 +1262,18 @@
       </c>
     </row>
     <row r="39" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="6"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="4" t="s">
         <v>35</v>
       </c>
@@ -1282,7 +1282,7 @@
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C41" s="3">

--- a/inputs/GRANAR_xml_inputs_generator.xlsx
+++ b/inputs/GRANAR_xml_inputs_generator.xlsx
@@ -1022,7 +1022,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="6">
-        <v>6.5080547641420863E-2</v>
+        <v>6.6454367340168949E-2</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -1037,17 +1037,17 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
-        <v>0.1</v>
+        <v>4.3492600000000001</v>
       </c>
       <c r="K9" s="3">
-        <v>6.6388079583631833E-4</v>
+        <v>1.9710071908292893E-3</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M9" s="15" t="str">
         <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
-        <v>&lt;central_xylem cell_diameter='0.0650805476414209' n_layers='1' n_files='1' order='1' cell_height='0.1' wall_thickness='0.000663880795836318' smoothness='0' /&gt;</v>
+        <v>&lt;central_xylem cell_diameter='0.0664543673401689' n_layers='1' n_files='1' order='1' cell_height='4.34926' wall_thickness='0.00197100719082929' smoothness='0.5' /&gt;</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
@@ -1055,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="6">
-        <v>1.5434881218981714E-2</v>
+        <v>1.281545857340427E-2</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -1068,17 +1068,17 @@
         <v>2</v>
       </c>
       <c r="J10" s="3">
-        <v>0.1</v>
+        <v>0.89558500000000008</v>
       </c>
       <c r="K10" s="3">
-        <v>6.0117126807696911E-4</v>
+        <v>1.2198383202520501E-3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="15" t="str">
         <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
-        <v>&lt;stele cell_diameter='0.0154348812189817' n_layers='3' order='2' cell_height='0.1' wall_thickness='0.000601171268076969' smoothness='0' /&gt;</v>
+        <v>&lt;stele cell_diameter='0.0128154585734043' n_layers='3' order='2' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -1086,7 +1086,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="6">
-        <v>2.5791226598235739E-2</v>
+        <v>1.8746694174762563E-2</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3">
@@ -1097,21 +1097,21 @@
         <v>1</v>
       </c>
       <c r="H11" s="3">
-        <v>6.4845210976397866E-2</v>
+        <v>6.4109381279242331E-2</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
-        <v>0.1</v>
+        <v>4.3492600000000001</v>
       </c>
       <c r="K11" s="3">
-        <v>6.6388079583631833E-4</v>
+        <v>1.8192371084292513E-3</v>
       </c>
       <c r="L11" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M11" s="15" t="str">
         <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
-        <v>&lt;xylem cell_diameter='0.0257912265982357' n_files='6' ratio='1' radius='0.0648452109763979' cell_height='0.1' wall_thickness='0.000663880795836318' smoothness='0' /&gt;</v>
+        <v>&lt;xylem cell_diameter='0.0187466941747626' n_files='6' ratio='1' radius='0.0641093812792423' cell_height='4.34926' wall_thickness='0.00181923710842925' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -1119,28 +1119,28 @@
         <v>37</v>
       </c>
       <c r="C12" s="6">
-        <v>2.1855963384970627E-2</v>
+        <v>1.8179399719623155E-2</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
-        <v>5.2620288286818258E-2</v>
+        <v>4.7832823549534449E-2</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
-        <v>0.1</v>
+        <v>4.3492600000000001</v>
       </c>
       <c r="K12" s="3">
-        <v>5.4329968007095638E-4</v>
+        <v>1.5072758749263753E-3</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M12" s="15" t="str">
         <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
-        <v>&lt;phloem cell_diameter='0.0218559633849706' radius='0.0526202882868183' cell_height='0.1' wall_thickness='0.000543299680070956' smoothness='0' /&gt;</v>
+        <v>&lt;phloem cell_diameter='0.0181793997196232' radius='0.0478328235495344' cell_height='4.34926' wall_thickness='0.00150727587492638' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -1148,7 +1148,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="6">
-        <v>8.9654204200658068E-3</v>
+        <v>9.9438748599348127E-3</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1159,17 +1159,17 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>0.1</v>
+        <v>0.89558500000000008</v>
       </c>
       <c r="K13" s="3">
-        <v>9.7028126130910167E-4</v>
+        <v>1.2198383202520501E-3</v>
       </c>
       <c r="L13" s="3">
         <v>0</v>
       </c>
       <c r="M13" s="15" t="str">
         <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
-        <v>&lt;companion_cell cell_diameter='0.00896542042006581' n_cells_per_phloem='3' cell_height='0.1' wall_thickness='0.000970281261309102' smoothness='0' /&gt;</v>
+        <v>&lt;companion_cell cell_diameter='0.00994387485993481' n_cells_per_phloem='3' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
@@ -1177,7 +1177,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>1.5794724550035725E-2</v>
+        <v>1.3968484478179595E-2</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1190,17 +1190,17 @@
         <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0.1</v>
+        <v>0.89558500000000008</v>
       </c>
       <c r="K14" s="3">
-        <v>6.478020414292725E-4</v>
+        <v>1.9165684407448998E-3</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M14" s="15" t="str">
         <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
-        <v>&lt;pericycle cell_diameter='0.0157947245500357' n_layers='1' order='3' cell_height='0.1' wall_thickness='0.000647802041429273' smoothness='0' /&gt;</v>
+        <v>&lt;pericycle cell_diameter='0.0139684844781796' n_layers='1' order='3' cell_height='0.895585' wall_thickness='0.0019165684407449' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
@@ -1208,7 +1208,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>2.0555721352800555E-2</v>
+        <v>2.0105290098002614E-2</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -1221,36 +1221,48 @@
         <v>4</v>
       </c>
       <c r="J15" s="3">
-        <v>0.1</v>
+        <v>0.89558500000000008</v>
       </c>
       <c r="K15" s="3">
-        <v>1.4191051385933761E-3</v>
+        <v>1.6834980689988495E-3</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M15" s="15" t="str">
         <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
-        <v>&lt;endodermis cell_diameter='0.0205557213528006' n_layers='1' order='4' cell_height='0.1' wall_thickness='0.00141910513859338' smoothness='0' /&gt;</v>
+        <v>&lt;endodermis cell_diameter='0.0201052900980026' n_layers='1' order='4' cell_height='0.895585' wall_thickness='0.00168349806899885' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="3"/>
+      <c r="C16" s="6">
+        <v>2.9386739113945411E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="I16" s="3">
+        <v>5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1.41299</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2.5592415026526364E-3</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
       <c r="M16" s="15" t="str">
         <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
-        <v/>
+        <v>&lt;inner_cortex cell_diameter='0.0293867391139454' n_layers='1' order='5' cell_height='1.41299' wall_thickness='0.00255924150265264' smoothness='1' /&gt;</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
@@ -1258,30 +1270,30 @@
         <v>32</v>
       </c>
       <c r="C17" s="6">
-        <v>4.2833218979241743E-2</v>
+        <v>5.386042387368277E-2</v>
       </c>
       <c r="D17" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="3">
-        <v>0.1</v>
+        <v>1.41299</v>
       </c>
       <c r="K17" s="3">
-        <v>1.0272272474293675E-3</v>
+        <v>2.5621041888972147E-3</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
       </c>
       <c r="M17" s="15" t="str">
         <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
-        <v>&lt;cortex cell_diameter='0.0428332189792417' n_layers='3' order='5' cell_height='0.1' wall_thickness='0.00102722724742937' smoothness='1' /&gt;</v>
+        <v>&lt;cortex cell_diameter='0.0538604238736828' n_layers='2' order='6' cell_height='1.41299' wall_thickness='0.00256210418889721' smoothness='1' /&gt;</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
@@ -1308,7 +1320,7 @@
         <v>34</v>
       </c>
       <c r="C19" s="6">
-        <v>5.0110040466455646E-2</v>
+        <v>0.04</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -1318,20 +1330,20 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J19" s="3">
-        <v>0.1</v>
+        <v>1.296576</v>
       </c>
       <c r="K19" s="3">
-        <v>2.1495314617567783E-3</v>
+        <v>4.1890642045656502E-3</v>
       </c>
       <c r="L19" s="3">
         <v>0.5</v>
       </c>
       <c r="M19" s="15" t="str">
         <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
-        <v>&lt;exodermis cell_diameter='0.0501100404664556' n_layers='1' order='6' cell_height='0.1' wall_thickness='0.00214953146175678' smoothness='0.5' /&gt;</v>
+        <v>&lt;exodermis cell_diameter='0.04' n_layers='1' order='8' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.5' /&gt;</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
@@ -1339,7 +1351,7 @@
         <v>35</v>
       </c>
       <c r="C20" s="6">
-        <v>4.3177605057073083E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -1349,20 +1361,20 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="3">
-        <v>0.1</v>
+        <v>1.296576</v>
       </c>
       <c r="K20" s="3">
-        <v>2.1157732342175933E-3</v>
+        <v>4.1890642045656502E-3</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M20" s="15" t="str">
         <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
-        <v>&lt;epidermis cell_diameter='0.0431776050570731' n_layers='1' order='7' cell_height='0.1' wall_thickness='0.00211577323421759' smoothness='0' /&gt;</v>
+        <v>&lt;epidermis cell_diameter='0.02' n_layers='1' order='9' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
@@ -1505,63 +1517,63 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="15" t="str">
         <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
-        <v>&lt;central_xylem cell_diameter='0.0650805476414209' n_layers='1' n_files='1' order='1' cell_height='0.1' wall_thickness='0.000663880795836318' smoothness='0' /&gt;</v>
+        <v>&lt;central_xylem cell_diameter='0.0664543673401689' n_layers='1' n_files='1' order='1' cell_height='4.34926' wall_thickness='0.00197100719082929' smoothness='0.5' /&gt;</v>
       </c>
       <c r="C12" s="18"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="15" t="str">
         <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
-        <v>&lt;stele cell_diameter='0.0154348812189817' n_layers='3' order='2' cell_height='0.1' wall_thickness='0.000601171268076969' smoothness='0' /&gt;</v>
+        <v>&lt;stele cell_diameter='0.0128154585734043' n_layers='3' order='2' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
       </c>
       <c r="C13" s="18"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="15" t="str">
         <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
-        <v>&lt;xylem cell_diameter='0.0257912265982357' n_files='6' ratio='1' radius='0.0648452109763979' cell_height='0.1' wall_thickness='0.000663880795836318' smoothness='0' /&gt;</v>
+        <v>&lt;xylem cell_diameter='0.0187466941747626' n_files='6' ratio='1' radius='0.0641093812792423' cell_height='4.34926' wall_thickness='0.00181923710842925' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C14" s="18"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="str">
         <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
-        <v>&lt;phloem cell_diameter='0.0218559633849706' radius='0.0526202882868183' cell_height='0.1' wall_thickness='0.000543299680070956' smoothness='0' /&gt;</v>
+        <v>&lt;phloem cell_diameter='0.0181793997196232' radius='0.0478328235495344' cell_height='4.34926' wall_thickness='0.00150727587492638' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C15" s="18"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="15" t="str">
         <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
-        <v>&lt;companion_cell cell_diameter='0.00896542042006581' n_cells_per_phloem='3' cell_height='0.1' wall_thickness='0.000970281261309102' smoothness='0' /&gt;</v>
+        <v>&lt;companion_cell cell_diameter='0.00994387485993481' n_cells_per_phloem='3' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
       </c>
       <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="str">
         <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
-        <v>&lt;pericycle cell_diameter='0.0157947245500357' n_layers='1' order='3' cell_height='0.1' wall_thickness='0.000647802041429273' smoothness='0' /&gt;</v>
+        <v>&lt;pericycle cell_diameter='0.0139684844781796' n_layers='1' order='3' cell_height='0.895585' wall_thickness='0.0019165684407449' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C17" s="18"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="str">
         <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
-        <v>&lt;endodermis cell_diameter='0.0205557213528006' n_layers='1' order='4' cell_height='0.1' wall_thickness='0.00141910513859338' smoothness='0' /&gt;</v>
+        <v>&lt;endodermis cell_diameter='0.0201052900980026' n_layers='1' order='4' cell_height='0.895585' wall_thickness='0.00168349806899885' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C18" s="18"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="15" t="str">
         <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
-        <v/>
+        <v>&lt;inner_cortex cell_diameter='0.0293867391139454' n_layers='1' order='5' cell_height='1.41299' wall_thickness='0.00255924150265264' smoothness='1' /&gt;</v>
       </c>
       <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="15" t="str">
         <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
-        <v>&lt;cortex cell_diameter='0.0428332189792417' n_layers='3' order='5' cell_height='0.1' wall_thickness='0.00102722724742937' smoothness='1' /&gt;</v>
+        <v>&lt;cortex cell_diameter='0.0538604238736828' n_layers='2' order='6' cell_height='1.41299' wall_thickness='0.00256210418889721' smoothness='1' /&gt;</v>
       </c>
       <c r="C20" s="18"/>
     </row>
@@ -1575,14 +1587,14 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="15" t="str">
         <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
-        <v>&lt;exodermis cell_diameter='0.0501100404664556' n_layers='1' order='6' cell_height='0.1' wall_thickness='0.00214953146175678' smoothness='0.5' /&gt;</v>
+        <v>&lt;exodermis cell_diameter='0.04' n_layers='1' order='8' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.5' /&gt;</v>
       </c>
       <c r="C22" s="18"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="15" t="str">
         <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
-        <v>&lt;epidermis cell_diameter='0.0431776050570731' n_layers='1' order='7' cell_height='0.1' wall_thickness='0.00211577323421759' smoothness='0' /&gt;</v>
+        <v>&lt;epidermis cell_diameter='0.02' n_layers='1' order='9' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C23" s="18"/>
     </row>

--- a/inputs/GRANAR_xml_inputs_generator.xlsx
+++ b/inputs/GRANAR_xml_inputs_generator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2172" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2172" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>&lt;granar&gt;</t>
   </si>
@@ -171,9 +171,6 @@
     <t>[Real number, in mm - Positions the center of the cell according to the center of the root section]</t>
   </si>
   <si>
-    <t>n_cells_per_phloem</t>
-  </si>
-  <si>
     <t>secondary growth</t>
   </si>
   <si>
@@ -184,6 +181,12 @@
   </si>
   <si>
     <t>&lt;?xml version='1.0' encoding='utf-8'?&gt;</t>
+  </si>
+  <si>
+    <t>protoxylem</t>
+  </si>
+  <si>
+    <t>n_cells_per_file</t>
   </si>
 </sst>
 </file>
@@ -646,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:N29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -662,10 +665,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>35</v>
@@ -732,7 +735,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>11</v>
@@ -768,7 +771,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>46</v>
@@ -792,7 +795,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="5">
-        <v>6.6454367340168949E-2</v>
+        <v>4.8168666396867774E-2</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -807,17 +810,17 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>4.3492600000000001</v>
+        <v>1.1877500000000001</v>
       </c>
       <c r="K9" s="2">
-        <v>1.9710071908292893E-3</v>
+        <v>3.4662359278097325E-3</v>
       </c>
       <c r="L9" s="2">
         <v>0.5</v>
       </c>
       <c r="M9" s="14" t="str">
-        <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
-        <v>&lt;central_xylem cell_diameter='0.0664543673401689' n_layers='1' n_files='1' order='1' cell_height='4.34926' wall_thickness='0.00197100719082929' smoothness='0.5' /&gt;</v>
+        <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_file='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
+        <v>&lt;central_xylem cell_diameter='0.0481686663968678' n_layers='1' n_files='1' order='1' cell_height='1.18775' wall_thickness='0.00346623592780973' smoothness='0.5' /&gt;</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
@@ -825,10 +828,10 @@
         <v>25</v>
       </c>
       <c r="C10" s="5">
-        <v>1.281545857340427E-2</v>
+        <v>8.3113148788225948E-3</v>
       </c>
       <c r="D10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -838,17 +841,17 @@
         <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>0.89558500000000008</v>
+        <v>0.26091250000000005</v>
       </c>
       <c r="K10" s="2">
-        <v>1.2198383202520501E-3</v>
+        <v>1.478088403091033E-3</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="14" t="str">
-        <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
-        <v>&lt;stele cell_diameter='0.0128154585734043' n_layers='3' order='2' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
+        <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_file='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
+        <v>&lt;stele cell_diameter='0.00831131487882259' n_layers='4' order='2' cell_height='0.2609125' wall_thickness='0.00147808840309103' smoothness='0' /&gt;</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -856,129 +859,127 @@
         <v>33</v>
       </c>
       <c r="C11" s="5">
-        <v>1.8746694174762563E-2</v>
+        <v>1.5230273220953114E-2</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2">
-        <v>6.4109381279242331E-2</v>
+        <v>5.3596133346265867E-2</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2">
-        <v>4.3492600000000001</v>
+        <v>0.32423000000000002</v>
       </c>
       <c r="K11" s="2">
-        <v>1.8192371084292513E-3</v>
+        <v>1.8621774020979196E-3</v>
       </c>
       <c r="L11" s="2">
         <v>0.2</v>
       </c>
       <c r="M11" s="14" t="str">
-        <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
-        <v>&lt;xylem cell_diameter='0.0187466941747626' n_files='6' ratio='1' radius='0.0641093812792423' cell_height='4.34926' wall_thickness='0.00181923710842925' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_file='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
+        <v>&lt;xylem cell_diameter='0.0152302732209531' n_files='7' radius='0.0535961333462659' cell_height='0.32423' wall_thickness='0.00186217740209792' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5">
-        <v>1.8179399719623155E-2</v>
+        <v>9.4611403199479169E-3</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2">
-        <v>4.7832823549534449E-2</v>
-      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2">
-        <v>4.3492600000000001</v>
+        <v>0.32423000000000002</v>
       </c>
       <c r="K12" s="2">
-        <v>1.5072758749263753E-3</v>
+        <v>2.3450171486833911E-3</v>
       </c>
       <c r="L12" s="2">
         <v>0.2</v>
       </c>
       <c r="M12" s="14" t="str">
-        <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
-        <v>&lt;phloem cell_diameter='0.0181793997196232' radius='0.0478328235495344' cell_height='4.34926' wall_thickness='0.00150727587492638' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_file='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
+        <v>&lt;protoxylem cell_diameter='0.00946114031994792' n_cells_per_file='1' cell_height='0.32423' wall_thickness='0.00234501714868339' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5">
-        <v>9.9438748599348127E-3</v>
+        <v>1.1002225997645431E-2</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
+      <c r="E13" s="2">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2">
+        <v>4.2372153280092612E-2</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2">
-        <v>0.89558500000000008</v>
+        <v>0.32423000000000002</v>
       </c>
       <c r="K13" s="2">
-        <v>1.2198383202520501E-3</v>
+        <v>1.8481025280620783E-3</v>
       </c>
       <c r="L13" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M13" s="14" t="str">
-        <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
-        <v>&lt;companion_cell cell_diameter='0.00994387485993481' n_cells_per_phloem='3' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
+        <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_file='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
+        <v>&lt;phloem cell_diameter='0.0110022259976454' n_files='7' radius='0.0423721532800926' cell_height='0.32423' wall_thickness='0.00184810252806208' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5">
-        <v>1.3968484478179595E-2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
+        <v>6.6759743044708941E-3</v>
+      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2">
-        <v>3</v>
-      </c>
+      <c r="I14" s="2"/>
       <c r="J14" s="2">
-        <v>0.89558500000000008</v>
+        <v>0.26091250000000005</v>
       </c>
       <c r="K14" s="2">
-        <v>1.9165684407448998E-3</v>
+        <v>1.478088403091033E-3</v>
       </c>
       <c r="L14" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="14" t="str">
-        <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
-        <v>&lt;pericycle cell_diameter='0.0139684844781796' n_layers='1' order='3' cell_height='0.895585' wall_thickness='0.0019165684407449' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_file='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
+        <v>&lt;companion_cell cell_diameter='0.00667597430447089' n_cells_per_file='3' cell_height='0.2609125' wall_thickness='0.00147808840309103' smoothness='0' /&gt;</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="5">
-        <v>2.0105290098002614E-2</v>
+        <v>1.4609987313075556E-2</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -986,30 +987,32 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2">
+        <v>6.6588777352092829E-2</v>
+      </c>
       <c r="I15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2">
-        <v>0.89558500000000008</v>
+        <v>0.26091250000000005</v>
       </c>
       <c r="K15" s="2">
-        <v>1.6834980689988495E-3</v>
+        <v>2.3450171486833911E-3</v>
       </c>
       <c r="L15" s="2">
         <v>0.2</v>
       </c>
       <c r="M15" s="14" t="str">
-        <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
-        <v>&lt;endodermis cell_diameter='0.0201052900980026' n_layers='1' order='4' cell_height='0.895585' wall_thickness='0.00168349806899885' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_file='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
+        <v>&lt;pericycle cell_diameter='0.0146099873130756' n_layers='1' radius='0.0665887773520928' order='3' cell_height='0.2609125' wall_thickness='0.00234501714868339' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5">
-        <v>2.9386739113945411E-2</v>
+        <v>2.1767831458071461E-2</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -1017,111 +1020,113 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2">
+        <v>8.1543130343671749E-2</v>
+      </c>
       <c r="I16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2">
-        <v>1.41299</v>
+        <v>0.26091250000000005</v>
       </c>
       <c r="K16" s="2">
-        <v>2.5592415026526364E-3</v>
+        <v>3.2634623188187981E-3</v>
       </c>
       <c r="L16" s="2">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M16" s="14" t="str">
-        <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
-        <v>&lt;inner_cortex cell_diameter='0.0293867391139454' n_layers='1' order='5' cell_height='1.41299' wall_thickness='0.00255924150265264' smoothness='1' /&gt;</v>
+        <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_file='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
+        <v>&lt;endodermis cell_diameter='0.0217678314580715' n_layers='1' radius='0.0815431303436717' order='4' cell_height='0.2609125' wall_thickness='0.0032634623188188' smoothness='0.2' /&gt;</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5">
-        <v>5.386042387368277E-2</v>
+        <v>2.8060885568272475E-2</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="2">
-        <v>1.41299</v>
+        <v>0.39289499999999999</v>
       </c>
       <c r="K17" s="2">
-        <v>2.5621041888972147E-3</v>
+        <v>2.7314797917014065E-3</v>
       </c>
       <c r="L17" s="2">
         <v>1</v>
       </c>
       <c r="M17" s="14" t="str">
-        <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
-        <v>&lt;cortex cell_diameter='0.0538604238736828' n_layers='2' order='6' cell_height='1.41299' wall_thickness='0.00256210418889721' smoothness='1' /&gt;</v>
+        <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_file='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
+        <v>&lt;inner_cortex cell_diameter='0.0280608855682725' n_layers='1' order='5' cell_height='0.392895' wall_thickness='0.00273147979170141' smoothness='1' /&gt;</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3.3436250377997231E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="I18" s="2">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.39289499999999999</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2.1276915512825193E-3</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
       <c r="M18" s="14" t="str">
-        <f>IF(SUM(INPUTS!D18:L18)&gt;0,CONCATENATE("&lt;",INPUTS!B18," cell_diameter='",INPUTS!C18,IF(INPUTS!D18="","",CONCATENATE("' n_layers='",INPUTS!D18)),IF(INPUTS!E18="","",CONCATENATE("' n_files='",INPUTS!E18)),IF(INPUTS!F18="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F18)),IF(INPUTS!G18="","",CONCATENATE("' ratio='",INPUTS!G18)),IF(INPUTS!H18="","",CONCATENATE("' radius='",INPUTS!H18)),IF(INPUTS!I18="","",CONCATENATE("' order='",INPUTS!I18)),IF(INPUTS!J18="","",CONCATENATE("' cell_height='",INPUTS!J18)),IF(INPUTS!K18="","",CONCATENATE("' wall_thickness='",INPUTS!K18)),IF(INPUTS!L18="","",CONCATENATE("' smoothness='",INPUTS!L18)),"' /&gt;"),"")</f>
-        <v/>
+        <f>IF(SUM(INPUTS!D18:L18)&gt;0,CONCATENATE("&lt;",INPUTS!B18," cell_diameter='",INPUTS!C18,IF(INPUTS!D18="","",CONCATENATE("' n_layers='",INPUTS!D18)),IF(INPUTS!E18="","",CONCATENATE("' n_files='",INPUTS!E18)),IF(INPUTS!F18="","",CONCATENATE("' n_cells_per_file='",INPUTS!F18)),IF(INPUTS!G18="","",CONCATENATE("' ratio='",INPUTS!G18)),IF(INPUTS!H18="","",CONCATENATE("' radius='",INPUTS!H18)),IF(INPUTS!I18="","",CONCATENATE("' order='",INPUTS!I18)),IF(INPUTS!J18="","",CONCATENATE("' cell_height='",INPUTS!J18)),IF(INPUTS!K18="","",CONCATENATE("' wall_thickness='",INPUTS!K18)),IF(INPUTS!L18="","",CONCATENATE("' smoothness='",INPUTS!L18)),"' /&gt;"),"")</f>
+        <v>&lt;cortex cell_diameter='0.0334362503779972' n_layers='2' order='6' cell_height='0.392895' wall_thickness='0.00212769155128252' smoothness='1' /&gt;</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1.296576</v>
-      </c>
-      <c r="K19" s="2">
-        <v>4.1890642045656502E-3</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.5</v>
-      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
       <c r="M19" s="14" t="str">
-        <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
-        <v>&lt;exodermis cell_diameter='0.04' n_layers='1' order='8' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.5' /&gt;</v>
+        <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_file='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
+        <v/>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="5">
-        <v>0.02</v>
+        <v>2.8752600183562023E-2</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -1129,108 +1134,141 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2">
+        <v>0.15523033258008867</v>
+      </c>
       <c r="I20" s="2">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.361568</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2.6241290575297355E-3</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="14" t="str">
+        <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_file='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
+        <v>&lt;exodermis cell_diameter='0.028752600183562' n_layers='1' radius='0.155230332580089' order='8' cell_height='0.361568' wall_thickness='0.00262412905752974' smoothness='0.5' /&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2.8752600183562023E-2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2">
         <v>9</v>
       </c>
-      <c r="J20" s="2">
-        <v>1.296576</v>
-      </c>
-      <c r="K20" s="2">
-        <v>4.1890642045656502E-3</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="M20" s="14" t="str">
-        <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
-        <v>&lt;epidermis cell_diameter='0.02' n_layers='1' order='9' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.2' /&gt;</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-    </row>
-    <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
+      <c r="J21" s="2">
+        <v>0.361568</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2.6241290575297355E-3</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="14" t="str">
+        <f>IF(SUM(INPUTS!D21:L21)&gt;0,CONCATENATE("&lt;",INPUTS!B21," cell_diameter='",INPUTS!C21,IF(INPUTS!D21="","",CONCATENATE("' n_layers='",INPUTS!D21)),IF(INPUTS!E21="","",CONCATENATE("' n_files='",INPUTS!E21)),IF(INPUTS!F21="","",CONCATENATE("' n_cells_per_file='",INPUTS!F21)),IF(INPUTS!G21="","",CONCATENATE("' ratio='",INPUTS!G21)),IF(INPUTS!H21="","",CONCATENATE("' radius='",INPUTS!H21)),IF(INPUTS!I21="","",CONCATENATE("' order='",INPUTS!I21)),IF(INPUTS!J21="","",CONCATENATE("' cell_height='",INPUTS!J21)),IF(INPUTS!K21="","",CONCATENATE("' wall_thickness='",INPUTS!K21)),IF(INPUTS!L21="","",CONCATENATE("' smoothness='",INPUTS!L21)),"' /&gt;"),"")</f>
+        <v>&lt;epidermis cell_diameter='0.028752600183562' n_layers='1' order='9' cell_height='0.361568' wall_thickness='0.00262412905752974' smoothness='0.5' /&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E22"/>
-    </row>
-    <row r="23" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="22"/>
-      <c r="C23" s="3" t="s">
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="22"/>
+      <c r="C24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C25" s="2">
         <v>0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D25" s="2">
         <v>10</v>
       </c>
-      <c r="E24" s="14" t="str">
-        <f>IF(SUM(C24:D24)=0,"",CONCATENATE("&lt;", B24, IF(C24="","",CONCATENATE(" proportion='",C24)),IF(C24="","",CONCATENATE("' n_files='",D24)),"' /&gt;"))</f>
+      <c r="E25" s="14" t="str">
+        <f>IF(SUM(C25:D25)=0,"",CONCATENATE("&lt;", B25, IF(C25="","",CONCATENATE(" proportion='",C25)),IF(C25="","",CONCATENATE("' n_files='",D25)),"' /&gt;"))</f>
         <v>&lt;aerenchyma proportion='0' n_files='10' /&gt;</v>
       </c>
-      <c r="F24"/>
-    </row>
-    <row r="26" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+      <c r="F25"/>
+    </row>
+    <row r="27" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="22"/>
-      <c r="C27" s="3" t="s">
+    <row r="28" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="22"/>
+      <c r="C28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="s">
+    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="14" t="str">
-        <f>IF(SUM(C28:D28)=0,"",CONCATENATE("&lt;", B28, IF(C28="","",CONCATENATE(" length='",C28)),IF(C28="","",CONCATENATE("' n_files='",D28)),"' /&gt;"))</f>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="14" t="str">
+        <f>IF(SUM(C29:D29)=0,"",CONCATENATE("&lt;", B29, IF(C29="","",CONCATENATE(" length='",C29)),IF(C29="","",CONCATENATE("' n_files='",D29)),"' /&gt;"))</f>
         <v/>
       </c>
-      <c r="I28"/>
-      <c r="N28" s="19"/>
+      <c r="I29"/>
+      <c r="N29" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B27:B28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1239,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="11.5546875" style="13"/>
@@ -1248,7 +1286,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1286,107 +1324,114 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="str">
-        <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
-        <v>&lt;central_xylem cell_diameter='0.0664543673401689' n_layers='1' n_files='1' order='1' cell_height='4.34926' wall_thickness='0.00197100719082929' smoothness='0.5' /&gt;</v>
+        <f>IF(SUM(INPUTS!D9:L9)&gt;0,CONCATENATE("&lt;",INPUTS!B9," cell_diameter='",INPUTS!C9,IF(INPUTS!D9="","",CONCATENATE("' n_layers='",INPUTS!D9)),IF(INPUTS!E9="","",CONCATENATE("' n_files='",INPUTS!E9)),IF(INPUTS!F9="","",CONCATENATE("' n_cells_per_file='",INPUTS!F9)),IF(INPUTS!G9="","",CONCATENATE("' ratio='",INPUTS!G9)),IF(INPUTS!H9="","",CONCATENATE("' radius='",INPUTS!H9)),IF(INPUTS!I9="","",CONCATENATE("' order='",INPUTS!I9)),IF(INPUTS!J9="","",CONCATENATE("' cell_height='",INPUTS!J9)),IF(INPUTS!K9="","",CONCATENATE("' wall_thickness='",INPUTS!K9)),IF(INPUTS!L9="","",CONCATENATE("' smoothness='",INPUTS!L9)),"' /&gt;"),"")</f>
+        <v>&lt;central_xylem cell_diameter='0.0481686663968678' n_layers='1' n_files='1' order='1' cell_height='1.18775' wall_thickness='0.00346623592780973' smoothness='0.5' /&gt;</v>
       </c>
       <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="str">
-        <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
-        <v>&lt;stele cell_diameter='0.0128154585734043' n_layers='3' order='2' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
+        <f>IF(SUM(INPUTS!D10:L10)&gt;0,CONCATENATE("&lt;",INPUTS!B10," cell_diameter='",INPUTS!C10,IF(INPUTS!D10="","",CONCATENATE("' n_layers='",INPUTS!D10)),IF(INPUTS!E10="","",CONCATENATE("' n_files='",INPUTS!E10)),IF(INPUTS!F10="","",CONCATENATE("' n_cells_per_file='",INPUTS!F10)),IF(INPUTS!G10="","",CONCATENATE("' ratio='",INPUTS!G10)),IF(INPUTS!H10="","",CONCATENATE("' radius='",INPUTS!H10)),IF(INPUTS!I10="","",CONCATENATE("' order='",INPUTS!I10)),IF(INPUTS!J10="","",CONCATENATE("' cell_height='",INPUTS!J10)),IF(INPUTS!K10="","",CONCATENATE("' wall_thickness='",INPUTS!K10)),IF(INPUTS!L10="","",CONCATENATE("' smoothness='",INPUTS!L10)),"' /&gt;"),"")</f>
+        <v>&lt;stele cell_diameter='0.00831131487882259' n_layers='4' order='2' cell_height='0.2609125' wall_thickness='0.00147808840309103' smoothness='0' /&gt;</v>
       </c>
       <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="str">
-        <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
-        <v>&lt;xylem cell_diameter='0.0187466941747626' n_files='6' ratio='1' radius='0.0641093812792423' cell_height='4.34926' wall_thickness='0.00181923710842925' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D11:L11)&gt;0,CONCATENATE("&lt;",INPUTS!B11," cell_diameter='",INPUTS!C11,IF(INPUTS!D11="","",CONCATENATE("' n_layers='",INPUTS!D11)),IF(INPUTS!E11="","",CONCATENATE("' n_files='",INPUTS!E11)),IF(INPUTS!F11="","",CONCATENATE("' n_cells_per_file='",INPUTS!F11)),IF(INPUTS!G11="","",CONCATENATE("' ratio='",INPUTS!G11)),IF(INPUTS!H11="","",CONCATENATE("' radius='",INPUTS!H11)),IF(INPUTS!I11="","",CONCATENATE("' order='",INPUTS!I11)),IF(INPUTS!J11="","",CONCATENATE("' cell_height='",INPUTS!J11)),IF(INPUTS!K11="","",CONCATENATE("' wall_thickness='",INPUTS!K11)),IF(INPUTS!L11="","",CONCATENATE("' smoothness='",INPUTS!L11)),"' /&gt;"),"")</f>
+        <v>&lt;xylem cell_diameter='0.0152302732209531' n_files='7' radius='0.0535961333462659' cell_height='0.32423' wall_thickness='0.00186217740209792' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C14" s="17"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="str">
-        <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
-        <v>&lt;phloem cell_diameter='0.0181793997196232' radius='0.0478328235495344' cell_height='4.34926' wall_thickness='0.00150727587492638' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D12:L12)&gt;0,CONCATENATE("&lt;",INPUTS!B12," cell_diameter='",INPUTS!C12,IF(INPUTS!D12="","",CONCATENATE("' n_layers='",INPUTS!D12)),IF(INPUTS!E12="","",CONCATENATE("' n_files='",INPUTS!E12)),IF(INPUTS!F12="","",CONCATENATE("' n_cells_per_file='",INPUTS!F12)),IF(INPUTS!G12="","",CONCATENATE("' ratio='",INPUTS!G12)),IF(INPUTS!H12="","",CONCATENATE("' radius='",INPUTS!H12)),IF(INPUTS!I12="","",CONCATENATE("' order='",INPUTS!I12)),IF(INPUTS!J12="","",CONCATENATE("' cell_height='",INPUTS!J12)),IF(INPUTS!K12="","",CONCATENATE("' wall_thickness='",INPUTS!K12)),IF(INPUTS!L12="","",CONCATENATE("' smoothness='",INPUTS!L12)),"' /&gt;"),"")</f>
+        <v>&lt;protoxylem cell_diameter='0.00946114031994792' n_cells_per_file='1' cell_height='0.32423' wall_thickness='0.00234501714868339' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C15" s="17"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="str">
-        <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
-        <v>&lt;companion_cell cell_diameter='0.00994387485993481' n_cells_per_phloem='3' cell_height='0.895585' wall_thickness='0.00121983832025205' smoothness='0' /&gt;</v>
+        <f>IF(SUM(INPUTS!D13:L13)&gt;0,CONCATENATE("&lt;",INPUTS!B13," cell_diameter='",INPUTS!C13,IF(INPUTS!D13="","",CONCATENATE("' n_layers='",INPUTS!D13)),IF(INPUTS!E13="","",CONCATENATE("' n_files='",INPUTS!E13)),IF(INPUTS!F13="","",CONCATENATE("' n_cells_per_file='",INPUTS!F13)),IF(INPUTS!G13="","",CONCATENATE("' ratio='",INPUTS!G13)),IF(INPUTS!H13="","",CONCATENATE("' radius='",INPUTS!H13)),IF(INPUTS!I13="","",CONCATENATE("' order='",INPUTS!I13)),IF(INPUTS!J13="","",CONCATENATE("' cell_height='",INPUTS!J13)),IF(INPUTS!K13="","",CONCATENATE("' wall_thickness='",INPUTS!K13)),IF(INPUTS!L13="","",CONCATENATE("' smoothness='",INPUTS!L13)),"' /&gt;"),"")</f>
+        <v>&lt;phloem cell_diameter='0.0110022259976454' n_files='7' radius='0.0423721532800926' cell_height='0.32423' wall_thickness='0.00184810252806208' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="str">
-        <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
-        <v>&lt;pericycle cell_diameter='0.0139684844781796' n_layers='1' order='3' cell_height='0.895585' wall_thickness='0.0019165684407449' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D14:L14)&gt;0,CONCATENATE("&lt;",INPUTS!B14," cell_diameter='",INPUTS!C14,IF(INPUTS!D14="","",CONCATENATE("' n_layers='",INPUTS!D14)),IF(INPUTS!E14="","",CONCATENATE("' n_files='",INPUTS!E14)),IF(INPUTS!F14="","",CONCATENATE("' n_cells_per_file='",INPUTS!F14)),IF(INPUTS!G14="","",CONCATENATE("' ratio='",INPUTS!G14)),IF(INPUTS!H14="","",CONCATENATE("' radius='",INPUTS!H14)),IF(INPUTS!I14="","",CONCATENATE("' order='",INPUTS!I14)),IF(INPUTS!J14="","",CONCATENATE("' cell_height='",INPUTS!J14)),IF(INPUTS!K14="","",CONCATENATE("' wall_thickness='",INPUTS!K14)),IF(INPUTS!L14="","",CONCATENATE("' smoothness='",INPUTS!L14)),"' /&gt;"),"")</f>
+        <v>&lt;companion_cell cell_diameter='0.00667597430447089' n_cells_per_file='3' cell_height='0.2609125' wall_thickness='0.00147808840309103' smoothness='0' /&gt;</v>
       </c>
       <c r="C17" s="17"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="str">
-        <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
-        <v>&lt;endodermis cell_diameter='0.0201052900980026' n_layers='1' order='4' cell_height='0.895585' wall_thickness='0.00168349806899885' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D15:L15)&gt;0,CONCATENATE("&lt;",INPUTS!B15," cell_diameter='",INPUTS!C15,IF(INPUTS!D15="","",CONCATENATE("' n_layers='",INPUTS!D15)),IF(INPUTS!E15="","",CONCATENATE("' n_files='",INPUTS!E15)),IF(INPUTS!F15="","",CONCATENATE("' n_cells_per_file='",INPUTS!F15)),IF(INPUTS!G15="","",CONCATENATE("' ratio='",INPUTS!G15)),IF(INPUTS!H15="","",CONCATENATE("' radius='",INPUTS!H15)),IF(INPUTS!I15="","",CONCATENATE("' order='",INPUTS!I15)),IF(INPUTS!J15="","",CONCATENATE("' cell_height='",INPUTS!J15)),IF(INPUTS!K15="","",CONCATENATE("' wall_thickness='",INPUTS!K15)),IF(INPUTS!L15="","",CONCATENATE("' smoothness='",INPUTS!L15)),"' /&gt;"),"")</f>
+        <v>&lt;pericycle cell_diameter='0.0146099873130756' n_layers='1' radius='0.0665887773520928' order='3' cell_height='0.2609125' wall_thickness='0.00234501714868339' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C18" s="17"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="str">
-        <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
-        <v>&lt;inner_cortex cell_diameter='0.0293867391139454' n_layers='1' order='5' cell_height='1.41299' wall_thickness='0.00255924150265264' smoothness='1' /&gt;</v>
+        <f>IF(SUM(INPUTS!D16:L16)&gt;0,CONCATENATE("&lt;",INPUTS!B16," cell_diameter='",INPUTS!C16,IF(INPUTS!D16="","",CONCATENATE("' n_layers='",INPUTS!D16)),IF(INPUTS!E16="","",CONCATENATE("' n_files='",INPUTS!E16)),IF(INPUTS!F16="","",CONCATENATE("' n_cells_per_file='",INPUTS!F16)),IF(INPUTS!G16="","",CONCATENATE("' ratio='",INPUTS!G16)),IF(INPUTS!H16="","",CONCATENATE("' radius='",INPUTS!H16)),IF(INPUTS!I16="","",CONCATENATE("' order='",INPUTS!I16)),IF(INPUTS!J16="","",CONCATENATE("' cell_height='",INPUTS!J16)),IF(INPUTS!K16="","",CONCATENATE("' wall_thickness='",INPUTS!K16)),IF(INPUTS!L16="","",CONCATENATE("' smoothness='",INPUTS!L16)),"' /&gt;"),"")</f>
+        <v>&lt;endodermis cell_diameter='0.0217678314580715' n_layers='1' radius='0.0815431303436717' order='4' cell_height='0.2609125' wall_thickness='0.0032634623188188' smoothness='0.2' /&gt;</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="14" t="str">
-        <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
-        <v>&lt;cortex cell_diameter='0.0538604238736828' n_layers='2' order='6' cell_height='1.41299' wall_thickness='0.00256210418889721' smoothness='1' /&gt;</v>
+        <f>IF(SUM(INPUTS!D17:L17)&gt;0,CONCATENATE("&lt;",INPUTS!B17," cell_diameter='",INPUTS!C17,IF(INPUTS!D17="","",CONCATENATE("' n_layers='",INPUTS!D17)),IF(INPUTS!E17="","",CONCATENATE("' n_files='",INPUTS!E17)),IF(INPUTS!F17="","",CONCATENATE("' n_cells_per_file='",INPUTS!F17)),IF(INPUTS!G17="","",CONCATENATE("' ratio='",INPUTS!G17)),IF(INPUTS!H17="","",CONCATENATE("' radius='",INPUTS!H17)),IF(INPUTS!I17="","",CONCATENATE("' order='",INPUTS!I17)),IF(INPUTS!J17="","",CONCATENATE("' cell_height='",INPUTS!J17)),IF(INPUTS!K17="","",CONCATENATE("' wall_thickness='",INPUTS!K17)),IF(INPUTS!L17="","",CONCATENATE("' smoothness='",INPUTS!L17)),"' /&gt;"),"")</f>
+        <v>&lt;inner_cortex cell_diameter='0.0280608855682725' n_layers='1' order='5' cell_height='0.392895' wall_thickness='0.00273147979170141' smoothness='1' /&gt;</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="str">
-        <f>IF(SUM(INPUTS!D18:L18)&gt;0,CONCATENATE("&lt;",INPUTS!B18," cell_diameter='",INPUTS!C18,IF(INPUTS!D18="","",CONCATENATE("' n_layers='",INPUTS!D18)),IF(INPUTS!E18="","",CONCATENATE("' n_files='",INPUTS!E18)),IF(INPUTS!F18="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F18)),IF(INPUTS!G18="","",CONCATENATE("' ratio='",INPUTS!G18)),IF(INPUTS!H18="","",CONCATENATE("' radius='",INPUTS!H18)),IF(INPUTS!I18="","",CONCATENATE("' order='",INPUTS!I18)),IF(INPUTS!J18="","",CONCATENATE("' cell_height='",INPUTS!J18)),IF(INPUTS!K18="","",CONCATENATE("' wall_thickness='",INPUTS!K18)),IF(INPUTS!L18="","",CONCATENATE("' smoothness='",INPUTS!L18)),"' /&gt;"),"")</f>
-        <v/>
+        <f>IF(SUM(INPUTS!D18:L18)&gt;0,CONCATENATE("&lt;",INPUTS!B18," cell_diameter='",INPUTS!C18,IF(INPUTS!D18="","",CONCATENATE("' n_layers='",INPUTS!D18)),IF(INPUTS!E18="","",CONCATENATE("' n_files='",INPUTS!E18)),IF(INPUTS!F18="","",CONCATENATE("' n_cells_per_file='",INPUTS!F18)),IF(INPUTS!G18="","",CONCATENATE("' ratio='",INPUTS!G18)),IF(INPUTS!H18="","",CONCATENATE("' radius='",INPUTS!H18)),IF(INPUTS!I18="","",CONCATENATE("' order='",INPUTS!I18)),IF(INPUTS!J18="","",CONCATENATE("' cell_height='",INPUTS!J18)),IF(INPUTS!K18="","",CONCATENATE("' wall_thickness='",INPUTS!K18)),IF(INPUTS!L18="","",CONCATENATE("' smoothness='",INPUTS!L18)),"' /&gt;"),"")</f>
+        <v>&lt;cortex cell_diameter='0.0334362503779972' n_layers='2' order='6' cell_height='0.392895' wall_thickness='0.00212769155128252' smoothness='1' /&gt;</v>
       </c>
       <c r="C21" s="17"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="str">
-        <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
-        <v>&lt;exodermis cell_diameter='0.04' n_layers='1' order='8' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.5' /&gt;</v>
+        <f>IF(SUM(INPUTS!D19:L19)&gt;0,CONCATENATE("&lt;",INPUTS!B19," cell_diameter='",INPUTS!C19,IF(INPUTS!D19="","",CONCATENATE("' n_layers='",INPUTS!D19)),IF(INPUTS!E19="","",CONCATENATE("' n_files='",INPUTS!E19)),IF(INPUTS!F19="","",CONCATENATE("' n_cells_per_file='",INPUTS!F19)),IF(INPUTS!G19="","",CONCATENATE("' ratio='",INPUTS!G19)),IF(INPUTS!H19="","",CONCATENATE("' radius='",INPUTS!H19)),IF(INPUTS!I19="","",CONCATENATE("' order='",INPUTS!I19)),IF(INPUTS!J19="","",CONCATENATE("' cell_height='",INPUTS!J19)),IF(INPUTS!K19="","",CONCATENATE("' wall_thickness='",INPUTS!K19)),IF(INPUTS!L19="","",CONCATENATE("' smoothness='",INPUTS!L19)),"' /&gt;"),"")</f>
+        <v/>
       </c>
       <c r="C22" s="17"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="str">
-        <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_phloem='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
-        <v>&lt;epidermis cell_diameter='0.02' n_layers='1' order='9' cell_height='1.296576' wall_thickness='0.00418906420456565' smoothness='0.2' /&gt;</v>
+        <f>IF(SUM(INPUTS!D20:L20)&gt;0,CONCATENATE("&lt;",INPUTS!B20," cell_diameter='",INPUTS!C20,IF(INPUTS!D20="","",CONCATENATE("' n_layers='",INPUTS!D20)),IF(INPUTS!E20="","",CONCATENATE("' n_files='",INPUTS!E20)),IF(INPUTS!F20="","",CONCATENATE("' n_cells_per_file='",INPUTS!F20)),IF(INPUTS!G20="","",CONCATENATE("' ratio='",INPUTS!G20)),IF(INPUTS!H20="","",CONCATENATE("' radius='",INPUTS!H20)),IF(INPUTS!I20="","",CONCATENATE("' order='",INPUTS!I20)),IF(INPUTS!J20="","",CONCATENATE("' cell_height='",INPUTS!J20)),IF(INPUTS!K20="","",CONCATENATE("' wall_thickness='",INPUTS!K20)),IF(INPUTS!L20="","",CONCATENATE("' smoothness='",INPUTS!L20)),"' /&gt;"),"")</f>
+        <v>&lt;exodermis cell_diameter='0.028752600183562' n_layers='1' radius='0.155230332580089' order='8' cell_height='0.361568' wall_thickness='0.00262412905752974' smoothness='0.5' /&gt;</v>
       </c>
       <c r="C23" s="17"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="13" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="14" t="str">
+        <f>IF(SUM(INPUTS!D21:L21)&gt;0,CONCATENATE("&lt;",INPUTS!B21," cell_diameter='",INPUTS!C21,IF(INPUTS!D21="","",CONCATENATE("' n_layers='",INPUTS!D21)),IF(INPUTS!E21="","",CONCATENATE("' n_files='",INPUTS!E21)),IF(INPUTS!F21="","",CONCATENATE("' n_cells_per_file='",INPUTS!F21)),IF(INPUTS!G21="","",CONCATENATE("' ratio='",INPUTS!G21)),IF(INPUTS!H21="","",CONCATENATE("' radius='",INPUTS!H21)),IF(INPUTS!I21="","",CONCATENATE("' order='",INPUTS!I21)),IF(INPUTS!J21="","",CONCATENATE("' cell_height='",INPUTS!J21)),IF(INPUTS!K21="","",CONCATENATE("' wall_thickness='",INPUTS!K21)),IF(INPUTS!L21="","",CONCATENATE("' smoothness='",INPUTS!L21)),"' /&gt;"),"")</f>
+        <v>&lt;epidermis cell_diameter='0.028752600183562' n_layers='1' order='9' cell_height='0.361568' wall_thickness='0.00262412905752974' smoothness='0.5' /&gt;</v>
+      </c>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="13" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="14" t="str">
-        <f>IF(SUM(INPUTS!C24:D24)=0,"",CONCATENATE("&lt;", INPUTS!B24, IF(INPUTS!C24="","",CONCATENATE(" proportion='",INPUTS!C24)),IF(INPUTS!C24="","",CONCATENATE("' n_files='",INPUTS!D24)),"' /&gt;"))</f>
-        <v>&lt;aerenchyma proportion='0' n_files='10' /&gt;</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="str">
-        <f>IF(SUM(INPUTS!C28:C28)=0,"",CONCATENATE("&lt;", INPUTS!B28, IF(INPUTS!C28="","",CONCATENATE(" length='",INPUTS!C28)),IF(INPUTS!C28="","",CONCATENATE("' n_files='",INPUTS!D28)),"' /&gt;"))</f>
+        <f>IF(SUM(INPUTS!C25:D25)=0,"",CONCATENATE("&lt;", INPUTS!B25, IF(INPUTS!C25="","",CONCATENATE(" proportion='",INPUTS!C25)),IF(INPUTS!C25="","",CONCATENATE("' n_files='",INPUTS!D25)),"' /&gt;"))</f>
+        <v>&lt;aerenchyma proportion='0' n_files='10' /&gt;</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="14" t="str">
+        <f>IF(SUM(INPUTS!C29:C29)=0,"",CONCATENATE("&lt;", INPUTS!B29, IF(INPUTS!C29="","",CONCATENATE(" length='",INPUTS!C29)),IF(INPUTS!C29="","",CONCATENATE("' n_files='",INPUTS!D29)),"' /&gt;"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>4</v>
       </c>
     </row>
